--- a/data/trans_orig/P33B_R1-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P33B_R1-Edad-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>19143</t>
+          <t>18590</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7027</t>
+          <t>7064</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>44953</t>
+          <t>36939</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>25655</t>
+          <t>34078</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13430</t>
+          <t>19828</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>42368</t>
+          <t>53722</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>44798</t>
+          <t>52668</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>27652</t>
+          <t>33910</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>70210</t>
+          <t>77303</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>10,04%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>380844</t>
+          <t>389203</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>355034</t>
+          <t>370854</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>392960</t>
+          <t>400729</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>287545</t>
+          <t>328434</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>270832</t>
+          <t>308790</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>299770</t>
+          <t>342684</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>90,6%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>85,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>668389</t>
+          <t>717637</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>642977</t>
+          <t>693002</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>685535</t>
+          <t>736395</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>95,6%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>25274</t>
+          <t>26585</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14817</t>
+          <t>15561</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>40895</t>
+          <t>41438</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>41202</t>
+          <t>43553</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24925</t>
+          <t>31058</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>56571</t>
+          <t>58247</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>66476</t>
+          <t>70138</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>48557</t>
+          <t>54979</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>87406</t>
+          <t>90284</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,23%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>398273</t>
+          <t>450305</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>382652</t>
+          <t>435452</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>408730</t>
+          <t>461329</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>470302</t>
+          <t>457530</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>454933</t>
+          <t>442836</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>486579</t>
+          <t>470025</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,94%</t>
+          <t>88,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>868575</t>
+          <t>907835</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>847645</t>
+          <t>887689</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>886494</t>
+          <t>922994</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,38%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>53678</t>
+          <t>57433</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>39707</t>
+          <t>42456</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>69756</t>
+          <t>75971</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>63380</t>
+          <t>73812</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>52074</t>
+          <t>61009</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>77255</t>
+          <t>89236</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>117058</t>
+          <t>131245</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>97703</t>
+          <t>110935</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>138044</t>
+          <t>154021</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,39%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>482660</t>
+          <t>563404</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>466582</t>
+          <t>544866</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>496631</t>
+          <t>578381</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>479088</t>
+          <t>548327</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>465213</t>
+          <t>532903</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>490394</t>
+          <t>561130</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>88,32%</t>
+          <t>88,14%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,76%</t>
+          <t>85,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>961748</t>
+          <t>1111731</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>940762</t>
+          <t>1088955</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>981103</t>
+          <t>1132041</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>89,44%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>87,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>91,08%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>83899</t>
+          <t>91496</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>38004</t>
+          <t>73349</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>124030</t>
+          <t>110343</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>133920</t>
+          <t>147829</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>110556</t>
+          <t>129564</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>152530</t>
+          <t>165313</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>217819</t>
+          <t>239324</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>137316</t>
+          <t>212753</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>267798</t>
+          <t>264650</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>18,42%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>803887</t>
+          <t>609121</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>763756</t>
+          <t>590274</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>849782</t>
+          <t>627268</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>86,94%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>84,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>89,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>578578</t>
+          <t>588666</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>559968</t>
+          <t>571182</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>601942</t>
+          <t>606931</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>81,2%</t>
+          <t>79,93%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,59%</t>
+          <t>77,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,48%</t>
+          <t>82,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1382466</t>
+          <t>1197788</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1332487</t>
+          <t>1172462</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1462969</t>
+          <t>1224359</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>86,39%</t>
+          <t>83,35%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,27%</t>
+          <t>81,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>85,2%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>712498</t>
+          <t>736495</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>712498</t>
+          <t>736495</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>712498</t>
+          <t>736495</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1600285</t>
+          <t>1437112</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1600285</t>
+          <t>1437112</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1600285</t>
+          <t>1437112</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>92731</t>
+          <t>97858</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>77123</t>
+          <t>82365</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>109081</t>
+          <t>117518</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>164391</t>
+          <t>187302</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>149390</t>
+          <t>169623</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>181043</t>
+          <t>205128</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>257122</t>
+          <t>285159</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>235394</t>
+          <t>262530</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>281679</t>
+          <t>310845</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,57%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>467473</t>
+          <t>510407</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>451123</t>
+          <t>490747</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>483081</t>
+          <t>525900</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>83,45%</t>
+          <t>83,91%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,53%</t>
+          <t>80,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,23%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>380672</t>
+          <t>420292</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>364020</t>
+          <t>402466</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>395673</t>
+          <t>437971</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>69,84%</t>
+          <t>69,17%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>66,78%</t>
+          <t>66,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>72,59%</t>
+          <t>72,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>848145</t>
+          <t>930699</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>823588</t>
+          <t>905013</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>869873</t>
+          <t>953328</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>76,74%</t>
+          <t>76,55%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>74,51%</t>
+          <t>74,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>78,7%</t>
+          <t>78,41%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>560204</t>
+          <t>608265</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>560204</t>
+          <t>608265</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>560204</t>
+          <t>608265</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>545063</t>
+          <t>607594</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>545063</t>
+          <t>607594</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>545063</t>
+          <t>607594</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1105267</t>
+          <t>1215858</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1105267</t>
+          <t>1215858</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1105267</t>
+          <t>1215858</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>67263</t>
+          <t>75001</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>56047</t>
+          <t>64199</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>79724</t>
+          <t>89734</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>115336</t>
+          <t>127611</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>45471</t>
+          <t>113839</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>180037</t>
+          <t>140839</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>182599</t>
+          <t>202611</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>92251</t>
+          <t>183810</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>237832</t>
+          <t>221866</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>26,24%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>300902</t>
+          <t>332079</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>288441</t>
+          <t>317346</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>312118</t>
+          <t>342881</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>81,73%</t>
+          <t>81,58%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>78,35%</t>
+          <t>77,96%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,78%</t>
+          <t>84,23%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>492466</t>
+          <t>310987</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>427765</t>
+          <t>297759</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>562331</t>
+          <t>324759</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>81,02%</t>
+          <t>70,9%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>70,38%</t>
+          <t>67,89%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>74,04%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>793369</t>
+          <t>643066</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>738136</t>
+          <t>623811</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>883717</t>
+          <t>661867</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>81,29%</t>
+          <t>76,04%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,63%</t>
+          <t>73,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>78,26%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>607802</t>
+          <t>438598</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>607802</t>
+          <t>438598</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>607802</t>
+          <t>438598</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>975968</t>
+          <t>845677</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>975968</t>
+          <t>845677</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>975968</t>
+          <t>845677</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>74257</t>
+          <t>82386</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>62868</t>
+          <t>70734</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>85739</t>
+          <t>96724</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>162175</t>
+          <t>179808</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>147943</t>
+          <t>164885</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>175463</t>
+          <t>195294</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>38,7%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>35,49%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>41,2%</t>
+          <t>42,03%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>236431</t>
+          <t>262194</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>218299</t>
+          <t>242217</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>255080</t>
+          <t>283980</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>36,0%</t>
+          <t>36,65%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>208502</t>
+          <t>227812</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>197020</t>
+          <t>213474</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>219891</t>
+          <t>239464</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>73,74%</t>
+          <t>73,44%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>69,68%</t>
+          <t>68,82%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>77,77%</t>
+          <t>77,2%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>263656</t>
+          <t>284801</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>250368</t>
+          <t>269315</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>277888</t>
+          <t>299724</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>61,92%</t>
+          <t>61,3%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>58,8%</t>
+          <t>57,97%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>65,26%</t>
+          <t>64,51%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>472159</t>
+          <t>512613</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>453510</t>
+          <t>490827</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>490291</t>
+          <t>532590</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>66,63%</t>
+          <t>66,16%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>64,0%</t>
+          <t>63,35%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>68,74%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,32 +3126,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>416243</t>
+          <t>449347</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>331078</t>
+          <t>410856</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>468750</t>
+          <t>488805</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,32 +3161,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>706060</t>
+          <t>793993</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>561591</t>
+          <t>752721</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>771546</t>
+          <t>835932</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1122303</t>
+          <t>1243340</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>975390</t>
+          <t>1183311</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1214311</t>
+          <t>1308982</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>18,02%</t>
         </is>
       </c>
     </row>
@@ -3239,32 +3239,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3042544</t>
+          <t>3082333</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2990037</t>
+          <t>3042875</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3127709</t>
+          <t>3120824</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>87,28%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>86,16%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>88,37%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,32 +3274,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2952306</t>
+          <t>2939037</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2886820</t>
+          <t>2897098</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3096775</t>
+          <t>2980309</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>80,7%</t>
+          <t>78,73%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>78,91%</t>
+          <t>77,61%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>84,65%</t>
+          <t>79,84%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>5994851</t>
+          <t>6021370</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5902843</t>
+          <t>5955728</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6141764</t>
+          <t>6081399</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>84,23%</t>
+          <t>82,89%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>82,94%</t>
+          <t>81,98%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>86,3%</t>
+          <t>83,71%</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3458787</t>
+          <t>3531680</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3458787</t>
+          <t>3531680</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3458787</t>
+          <t>3531680</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3658366</t>
+          <t>3733030</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3658366</t>
+          <t>3733030</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3658366</t>
+          <t>3733030</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7117154</t>
+          <t>7264710</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7117154</t>
+          <t>7264710</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7117154</t>
+          <t>7264710</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
